--- a/04-reformulacion/Presupuesto-marketing-AndiBite.xlsx
+++ b/04-reformulacion/Presupuesto-marketing-AndiBite.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">Pauta de expectativa</t>
   </si>
   <si>
-    <t xml:space="preserve">Instagram y TikTok</t>
+    <t xml:space="preserve">Instagram y Facebook</t>
   </si>
   <si>
     <t xml:space="preserve">Lanzamiento (inversión)</t>
